--- a/artfynd/A 1888-2025 artfynd.xlsx
+++ b/artfynd/A 1888-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122263308</v>
+        <v>122263390</v>
       </c>
       <c r="B2" t="n">
-        <v>57744</v>
+        <v>92055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632181</v>
+        <v>632166</v>
       </c>
       <c r="R2" t="n">
-        <v>6557398</v>
+        <v>6557511</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122263275</v>
+        <v>122263367</v>
       </c>
       <c r="B3" t="n">
-        <v>94947</v>
+        <v>92055</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,27 +802,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632119</v>
+        <v>632224</v>
       </c>
       <c r="R3" t="n">
-        <v>6557502</v>
+        <v>6557478</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,7 +869,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122263367</v>
+        <v>122263329</v>
       </c>
       <c r="B4" t="n">
-        <v>92055</v>
+        <v>5489</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,30 +909,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -949,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632224</v>
+        <v>632303</v>
       </c>
       <c r="R4" t="n">
-        <v>6557478</v>
+        <v>6557345</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,7 +986,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Gnagspår i barken på gammal senvuxen tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1128,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122263329</v>
+        <v>122263382</v>
       </c>
       <c r="B6" t="n">
-        <v>5489</v>
+        <v>92090</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,32 +1141,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101410</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1177,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632303</v>
+        <v>632252</v>
       </c>
       <c r="R6" t="n">
-        <v>6557345</v>
+        <v>6557554</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,7 +1216,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal senvuxen tall.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,17 +1237,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122263390</v>
+        <v>122263275</v>
       </c>
       <c r="B7" t="n">
-        <v>92055</v>
+        <v>94947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,26 +1260,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632166</v>
+        <v>632119</v>
       </c>
       <c r="R7" t="n">
-        <v>6557511</v>
+        <v>6557502</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122263382</v>
+        <v>122263308</v>
       </c>
       <c r="B8" t="n">
-        <v>92090</v>
+        <v>57744</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,25 +1368,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1394,12 +1394,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1407,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632252</v>
+        <v>632181</v>
       </c>
       <c r="R8" t="n">
-        <v>6557554</v>
+        <v>6557398</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1447,7 +1448,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,7 +1457,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 1888-2025 artfynd.xlsx
+++ b/artfynd/A 1888-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122263390</v>
+        <v>122263382</v>
       </c>
       <c r="B2" t="n">
-        <v>92055</v>
+        <v>92100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,29 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632166</v>
+        <v>632252</v>
       </c>
       <c r="R2" t="n">
-        <v>6557511</v>
+        <v>6557554</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -779,17 +787,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122263367</v>
+        <v>122263329</v>
       </c>
       <c r="B3" t="n">
-        <v>92055</v>
+        <v>5489</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +806,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632224</v>
+        <v>632303</v>
       </c>
       <c r="R3" t="n">
-        <v>6557478</v>
+        <v>6557345</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,7 +883,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Gnagspår i barken på gammal senvuxen tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122263329</v>
+        <v>122263377</v>
       </c>
       <c r="B4" t="n">
-        <v>5489</v>
+        <v>92065</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,36 +923,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632303</v>
+        <v>632243</v>
       </c>
       <c r="R4" t="n">
-        <v>6557345</v>
+        <v>6557542</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +994,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal senvuxen tall.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122263377</v>
+        <v>122263275</v>
       </c>
       <c r="B5" t="n">
-        <v>92055</v>
+        <v>94957</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,26 +1038,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1057,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632243</v>
+        <v>632119</v>
       </c>
       <c r="R5" t="n">
-        <v>6557542</v>
+        <v>6557502</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1106,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122263382</v>
+        <v>122263367</v>
       </c>
       <c r="B6" t="n">
-        <v>92090</v>
+        <v>92065</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,37 +1146,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1176,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632252</v>
+        <v>632224</v>
       </c>
       <c r="R6" t="n">
-        <v>6557554</v>
+        <v>6557478</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1237,17 +1238,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122263275</v>
+        <v>122263308</v>
       </c>
       <c r="B7" t="n">
-        <v>94947</v>
+        <v>57744</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,27 +1261,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1288,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632119</v>
+        <v>632181</v>
       </c>
       <c r="R7" t="n">
-        <v>6557502</v>
+        <v>6557398</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,7 +1337,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
+          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,7 +1346,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1356,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122263308</v>
+        <v>122263390</v>
       </c>
       <c r="B8" t="n">
-        <v>57744</v>
+        <v>92065</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,35 +1380,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1408,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632181</v>
+        <v>632166</v>
       </c>
       <c r="R8" t="n">
-        <v>6557398</v>
+        <v>6557511</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1448,7 +1447,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,6 +1456,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1888-2025 artfynd.xlsx
+++ b/artfynd/A 1888-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122263382</v>
+        <v>122263377</v>
       </c>
       <c r="B2" t="n">
-        <v>92100</v>
+        <v>92065</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -726,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632252</v>
+        <v>632243</v>
       </c>
       <c r="R2" t="n">
-        <v>6557554</v>
+        <v>6557542</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -787,17 +779,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122263329</v>
+        <v>122263275</v>
       </c>
       <c r="B3" t="n">
-        <v>5489</v>
+        <v>94957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,36 +798,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101410</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632303</v>
+        <v>632119</v>
       </c>
       <c r="R3" t="n">
-        <v>6557345</v>
+        <v>6557502</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal senvuxen tall.</t>
+          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122263377</v>
+        <v>122263329</v>
       </c>
       <c r="B4" t="n">
-        <v>92065</v>
+        <v>5489</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,30 +910,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632243</v>
+        <v>632303</v>
       </c>
       <c r="R4" t="n">
-        <v>6557542</v>
+        <v>6557345</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,7 +987,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Gnagspår i barken på gammal senvuxen tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122263275</v>
+        <v>122263308</v>
       </c>
       <c r="B5" t="n">
-        <v>94957</v>
+        <v>57744</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,27 +1031,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632119</v>
+        <v>632181</v>
       </c>
       <c r="R5" t="n">
-        <v>6557502</v>
+        <v>6557398</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1106,7 +1107,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
+          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1116,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122263308</v>
+        <v>122263382</v>
       </c>
       <c r="B7" t="n">
-        <v>57744</v>
+        <v>92100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,25 +1257,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1283,13 +1283,12 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1297,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632181</v>
+        <v>632252</v>
       </c>
       <c r="R7" t="n">
-        <v>6557398</v>
+        <v>6557554</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1337,7 +1336,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,6 +1345,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 1888-2025 artfynd.xlsx
+++ b/artfynd/A 1888-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122263377</v>
+        <v>122263390</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92077</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632243</v>
+        <v>632166</v>
       </c>
       <c r="R2" t="n">
-        <v>6557542</v>
+        <v>6557511</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122263275</v>
+        <v>122263329</v>
       </c>
       <c r="B3" t="n">
-        <v>94957</v>
+        <v>5489</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,31 +798,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>101410</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632119</v>
+        <v>632303</v>
       </c>
       <c r="R3" t="n">
-        <v>6557502</v>
+        <v>6557345</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +875,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
+          <t>Gnagspår i barken på gammal senvuxen tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122263329</v>
+        <v>122263382</v>
       </c>
       <c r="B4" t="n">
-        <v>5489</v>
+        <v>92112</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,32 +919,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101410</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632303</v>
+        <v>632252</v>
       </c>
       <c r="R4" t="n">
-        <v>6557345</v>
+        <v>6557554</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,7 +994,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal senvuxen tall.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,17 +1015,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122263308</v>
+        <v>122263275</v>
       </c>
       <c r="B5" t="n">
-        <v>57744</v>
+        <v>94969</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,35 +1038,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632181</v>
+        <v>632119</v>
       </c>
       <c r="R5" t="n">
-        <v>6557398</v>
+        <v>6557502</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,7 +1106,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
+          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,6 +1115,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122263367</v>
+        <v>122263308</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>57749</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,26 +1150,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1177,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632224</v>
+        <v>632181</v>
       </c>
       <c r="R6" t="n">
-        <v>6557478</v>
+        <v>6557398</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,7 +1226,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,7 +1235,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1245,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122263382</v>
+        <v>122263377</v>
       </c>
       <c r="B7" t="n">
-        <v>92100</v>
+        <v>92077</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,37 +1265,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632252</v>
+        <v>632243</v>
       </c>
       <c r="R7" t="n">
-        <v>6557554</v>
+        <v>6557542</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1357,17 +1357,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122263390</v>
+        <v>122263367</v>
       </c>
       <c r="B8" t="n">
-        <v>92065</v>
+        <v>92077</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632166</v>
+        <v>632224</v>
       </c>
       <c r="R8" t="n">
-        <v>6557511</v>
+        <v>6557478</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 1888-2025 artfynd.xlsx
+++ b/artfynd/A 1888-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122263390</v>
+        <v>122263275</v>
       </c>
       <c r="B2" t="n">
-        <v>92077</v>
+        <v>94974</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632166</v>
+        <v>632119</v>
       </c>
       <c r="R2" t="n">
-        <v>6557511</v>
+        <v>6557502</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -903,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122263382</v>
+        <v>122263390</v>
       </c>
       <c r="B4" t="n">
-        <v>92112</v>
+        <v>92082</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,37 +916,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -954,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632252</v>
+        <v>632166</v>
       </c>
       <c r="R4" t="n">
-        <v>6557554</v>
+        <v>6557511</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1015,17 +1008,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122263275</v>
+        <v>122263377</v>
       </c>
       <c r="B5" t="n">
-        <v>94969</v>
+        <v>92082</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,27 +1031,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632119</v>
+        <v>632243</v>
       </c>
       <c r="R5" t="n">
-        <v>6557502</v>
+        <v>6557542</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1106,7 +1098,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122263308</v>
+        <v>122263367</v>
       </c>
       <c r="B6" t="n">
-        <v>57749</v>
+        <v>92082</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,35 +1142,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1186,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632181</v>
+        <v>632224</v>
       </c>
       <c r="R6" t="n">
-        <v>6557398</v>
+        <v>6557478</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1226,7 +1209,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,6 +1218,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1253,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122263377</v>
+        <v>122263382</v>
       </c>
       <c r="B7" t="n">
-        <v>92077</v>
+        <v>92117</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,29 +1249,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1296,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632243</v>
+        <v>632252</v>
       </c>
       <c r="R7" t="n">
-        <v>6557542</v>
+        <v>6557554</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1357,17 +1349,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122263367</v>
+        <v>122263308</v>
       </c>
       <c r="B8" t="n">
-        <v>92077</v>
+        <v>57749</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,26 +1372,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1407,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632224</v>
+        <v>632181</v>
       </c>
       <c r="R8" t="n">
-        <v>6557478</v>
+        <v>6557398</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1447,7 +1448,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,7 +1457,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1888-2025 artfynd.xlsx
+++ b/artfynd/A 1888-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122263275</v>
       </c>
       <c r="B2" t="n">
-        <v>94974</v>
+        <v>94983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>2180</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122263329</v>
+        <v>122263308</v>
       </c>
       <c r="B3" t="n">
-        <v>5489</v>
+        <v>57749</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,34 +794,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101410</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Reliktbock</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -836,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632303</v>
+        <v>632181</v>
       </c>
       <c r="R3" t="n">
-        <v>6557345</v>
+        <v>6557398</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +869,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal senvuxen tall.</t>
+          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -907,7 +899,7 @@
         <v>122263390</v>
       </c>
       <c r="B4" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,11 +913,6 @@
       </c>
       <c r="E4" t="n">
         <v>4364</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1018,7 +1005,7 @@
         <v>122263377</v>
       </c>
       <c r="B5" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,11 +1019,6 @@
       </c>
       <c r="E5" t="n">
         <v>4364</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1129,7 +1111,7 @@
         <v>122263367</v>
       </c>
       <c r="B6" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,11 +1125,6 @@
       </c>
       <c r="E6" t="n">
         <v>4364</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1237,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122263382</v>
+        <v>122263329</v>
       </c>
       <c r="B7" t="n">
-        <v>92117</v>
+        <v>5489</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,34 +1230,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
+        <v>101410</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1288,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632252</v>
+        <v>632303</v>
       </c>
       <c r="R7" t="n">
-        <v>6557554</v>
+        <v>6557345</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,7 +1298,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Gnagspår i barken på gammal senvuxen tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,17 +1319,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122263308</v>
+        <v>122263382</v>
       </c>
       <c r="B8" t="n">
-        <v>57749</v>
+        <v>92122</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,25 +1338,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>5966</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1394,13 +1359,12 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1408,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632181</v>
+        <v>632252</v>
       </c>
       <c r="R8" t="n">
-        <v>6557398</v>
+        <v>6557554</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1448,7 +1412,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,6 +1421,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1468,7 +1433,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1492,11 +1457,6 @@
       </c>
       <c r="E9" t="n">
         <v>105930</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1573,11 +1533,6 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK9" t="inlineStr">
         <is>
           <t>Picea abies</t>

--- a/artfynd/A 1888-2025 artfynd.xlsx
+++ b/artfynd/A 1888-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122263275</v>
+        <v>122263367</v>
       </c>
       <c r="B2" t="n">
-        <v>94983</v>
+        <v>92100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,22 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>4364</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632119</v>
+        <v>632224</v>
       </c>
       <c r="R2" t="n">
-        <v>6557502</v>
+        <v>6557478</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +789,7 @@
         <v>122263308</v>
       </c>
       <c r="B3" t="n">
-        <v>57749</v>
+        <v>57753</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,6 +803,11 @@
       </c>
       <c r="E3" t="n">
         <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -896,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122263390</v>
+        <v>122263382</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>92135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,24 +917,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -934,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632166</v>
+        <v>632252</v>
       </c>
       <c r="R4" t="n">
-        <v>6557511</v>
+        <v>6557554</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,17 +1017,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122263377</v>
+        <v>122263390</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>92100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,6 +1041,11 @@
       </c>
       <c r="E5" t="n">
         <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1040,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632243</v>
+        <v>632166</v>
       </c>
       <c r="R5" t="n">
-        <v>6557542</v>
+        <v>6557511</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1108,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122263367</v>
+        <v>122263377</v>
       </c>
       <c r="B6" t="n">
-        <v>92087</v>
+        <v>92100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,6 +1152,11 @@
       </c>
       <c r="E6" t="n">
         <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1146,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632224</v>
+        <v>632243</v>
       </c>
       <c r="R6" t="n">
-        <v>6557478</v>
+        <v>6557542</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1232,6 +1264,11 @@
       <c r="E7" t="n">
         <v>101410</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Nothorhina muricata</t>
@@ -1326,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122263382</v>
+        <v>122263275</v>
       </c>
       <c r="B8" t="n">
-        <v>92122</v>
+        <v>94996</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,33 +1375,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>2180</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1372,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632252</v>
+        <v>632119</v>
       </c>
       <c r="R8" t="n">
-        <v>6557554</v>
+        <v>6557502</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1412,7 +1447,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,7 +1468,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1457,6 +1492,11 @@
       </c>
       <c r="E9" t="n">
         <v>105930</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1533,6 +1573,11 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK9" t="inlineStr">
         <is>
           <t>Picea abies</t>

--- a/artfynd/A 1888-2025 artfynd.xlsx
+++ b/artfynd/A 1888-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122263367</v>
+        <v>122263390</v>
       </c>
       <c r="B2" t="n">
-        <v>92100</v>
+        <v>92113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632224</v>
+        <v>632166</v>
       </c>
       <c r="R2" t="n">
-        <v>6557478</v>
+        <v>6557511</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122263308</v>
+        <v>122263377</v>
       </c>
       <c r="B3" t="n">
-        <v>57753</v>
+        <v>92113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +802,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632181</v>
+        <v>632243</v>
       </c>
       <c r="R3" t="n">
-        <v>6557398</v>
+        <v>6557542</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,7 +869,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,6 +878,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122263382</v>
+        <v>122263329</v>
       </c>
       <c r="B4" t="n">
-        <v>92135</v>
+        <v>5489</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,34 +913,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>101410</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632252</v>
+        <v>632303</v>
       </c>
       <c r="R4" t="n">
-        <v>6557554</v>
+        <v>6557345</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,7 +986,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Gnagspår i barken på gammal senvuxen tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,17 +1007,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122263390</v>
+        <v>122263308</v>
       </c>
       <c r="B5" t="n">
-        <v>92100</v>
+        <v>57753</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,26 +1030,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632166</v>
+        <v>632181</v>
       </c>
       <c r="R5" t="n">
-        <v>6557511</v>
+        <v>6557398</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,7 +1106,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1115,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1135,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122263377</v>
+        <v>122263382</v>
       </c>
       <c r="B6" t="n">
-        <v>92100</v>
+        <v>92148</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,29 +1145,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1178,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632243</v>
+        <v>632252</v>
       </c>
       <c r="R6" t="n">
-        <v>6557542</v>
+        <v>6557554</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1239,17 +1245,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122263329</v>
+        <v>122263367</v>
       </c>
       <c r="B7" t="n">
-        <v>5489</v>
+        <v>92113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,36 +1264,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632303</v>
+        <v>632224</v>
       </c>
       <c r="R7" t="n">
-        <v>6557345</v>
+        <v>6557478</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal senvuxen tall.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,7 +1366,7 @@
         <v>122263275</v>
       </c>
       <c r="B8" t="n">
-        <v>94996</v>
+        <v>95009</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 1888-2025 artfynd.xlsx
+++ b/artfynd/A 1888-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122263390</v>
+        <v>122263308</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>57753</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632166</v>
+        <v>632181</v>
       </c>
       <c r="R2" t="n">
-        <v>6557511</v>
+        <v>6557398</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,7 +767,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,7 +776,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122263377</v>
+        <v>122263275</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>95009</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,26 +810,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632243</v>
+        <v>632119</v>
       </c>
       <c r="R3" t="n">
-        <v>6557542</v>
+        <v>6557502</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,7 +878,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1014,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122263308</v>
+        <v>122263377</v>
       </c>
       <c r="B5" t="n">
-        <v>57753</v>
+        <v>92113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,35 +1039,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632181</v>
+        <v>632243</v>
       </c>
       <c r="R5" t="n">
-        <v>6557398</v>
+        <v>6557542</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,6 +1115,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1133,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122263382</v>
+        <v>122263367</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,37 +1146,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1184,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632252</v>
+        <v>632224</v>
       </c>
       <c r="R6" t="n">
-        <v>6557554</v>
+        <v>6557478</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1245,17 +1238,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122263367</v>
+        <v>122263382</v>
       </c>
       <c r="B7" t="n">
-        <v>92113</v>
+        <v>92148</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,29 +1257,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1295,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632224</v>
+        <v>632252</v>
       </c>
       <c r="R7" t="n">
-        <v>6557478</v>
+        <v>6557554</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1356,17 +1357,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122263275</v>
+        <v>122263390</v>
       </c>
       <c r="B8" t="n">
-        <v>95009</v>
+        <v>92113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,27 +1380,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632119</v>
+        <v>632166</v>
       </c>
       <c r="R8" t="n">
-        <v>6557502</v>
+        <v>6557511</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 1888-2025 artfynd.xlsx
+++ b/artfynd/A 1888-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122263308</v>
+        <v>122263275</v>
       </c>
       <c r="B2" t="n">
-        <v>57753</v>
+        <v>95011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632181</v>
+        <v>632119</v>
       </c>
       <c r="R2" t="n">
-        <v>6557398</v>
+        <v>6557502</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
+          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +768,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122263275</v>
+        <v>122263329</v>
       </c>
       <c r="B3" t="n">
-        <v>95009</v>
+        <v>5489</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +799,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>101410</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632119</v>
+        <v>632303</v>
       </c>
       <c r="R3" t="n">
-        <v>6557502</v>
+        <v>6557345</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
+          <t>Gnagspår i barken på gammal senvuxen tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122263329</v>
+        <v>122263377</v>
       </c>
       <c r="B4" t="n">
-        <v>5489</v>
+        <v>92114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,36 +916,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632303</v>
+        <v>632243</v>
       </c>
       <c r="R4" t="n">
-        <v>6557345</v>
+        <v>6557542</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,7 +987,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal senvuxen tall.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122263377</v>
+        <v>122263308</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>57753</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,26 +1031,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632243</v>
+        <v>632181</v>
       </c>
       <c r="R5" t="n">
-        <v>6557542</v>
+        <v>6557398</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1106,7 +1107,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1116,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122263367</v>
+        <v>122263382</v>
       </c>
       <c r="B6" t="n">
-        <v>92113</v>
+        <v>92149</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,29 +1146,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1177,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632224</v>
+        <v>632252</v>
       </c>
       <c r="R6" t="n">
-        <v>6557478</v>
+        <v>6557554</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1238,17 +1246,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122263382</v>
+        <v>122263390</v>
       </c>
       <c r="B7" t="n">
-        <v>92148</v>
+        <v>92114</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,37 +1265,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632252</v>
+        <v>632166</v>
       </c>
       <c r="R7" t="n">
-        <v>6557554</v>
+        <v>6557511</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1357,17 +1357,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122263390</v>
+        <v>122263367</v>
       </c>
       <c r="B8" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632166</v>
+        <v>632224</v>
       </c>
       <c r="R8" t="n">
-        <v>6557511</v>
+        <v>6557478</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 1888-2025 artfynd.xlsx
+++ b/artfynd/A 1888-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122263275</v>
+        <v>122263390</v>
       </c>
       <c r="B2" t="n">
-        <v>95011</v>
+        <v>92114</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632119</v>
+        <v>632166</v>
       </c>
       <c r="R2" t="n">
-        <v>6557502</v>
+        <v>6557511</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122263329</v>
+        <v>122263367</v>
       </c>
       <c r="B3" t="n">
-        <v>5489</v>
+        <v>92114</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,36 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632303</v>
+        <v>632224</v>
       </c>
       <c r="R3" t="n">
-        <v>6557345</v>
+        <v>6557478</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +869,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal senvuxen tall.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122263377</v>
+        <v>122263382</v>
       </c>
       <c r="B4" t="n">
-        <v>92114</v>
+        <v>92149</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,29 +909,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -947,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632243</v>
+        <v>632252</v>
       </c>
       <c r="R4" t="n">
-        <v>6557542</v>
+        <v>6557554</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,17 +1009,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122263308</v>
+        <v>122263329</v>
       </c>
       <c r="B5" t="n">
-        <v>57753</v>
+        <v>5489</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,37 +1028,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>101410</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1067,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632181</v>
+        <v>632303</v>
       </c>
       <c r="R5" t="n">
-        <v>6557398</v>
+        <v>6557345</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,7 +1105,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
+          <t>Gnagspår i barken på gammal senvuxen tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,6 +1114,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122263382</v>
+        <v>122263308</v>
       </c>
       <c r="B6" t="n">
-        <v>92149</v>
+        <v>57753</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,25 +1145,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1172,12 +1171,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632252</v>
+        <v>632181</v>
       </c>
       <c r="R6" t="n">
-        <v>6557554</v>
+        <v>6557398</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,7 +1234,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1246,17 +1245,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122263390</v>
+        <v>122263275</v>
       </c>
       <c r="B7" t="n">
-        <v>92114</v>
+        <v>95011</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,26 +1268,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632166</v>
+        <v>632119</v>
       </c>
       <c r="R7" t="n">
-        <v>6557511</v>
+        <v>6557502</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,7 +1364,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122263367</v>
+        <v>122263377</v>
       </c>
       <c r="B8" t="n">
         <v>92114</v>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632224</v>
+        <v>632243</v>
       </c>
       <c r="R8" t="n">
-        <v>6557478</v>
+        <v>6557542</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 1888-2025 artfynd.xlsx
+++ b/artfynd/A 1888-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122263390</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122263367</v>
+        <v>122263329</v>
       </c>
       <c r="B3" t="n">
-        <v>92114</v>
+        <v>5489</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +798,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632224</v>
+        <v>632303</v>
       </c>
       <c r="R3" t="n">
-        <v>6557478</v>
+        <v>6557345</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,7 +875,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Gnagspår i barken på gammal senvuxen tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122263382</v>
+        <v>122263367</v>
       </c>
       <c r="B4" t="n">
-        <v>92149</v>
+        <v>92115</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,37 +915,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -948,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632252</v>
+        <v>632224</v>
       </c>
       <c r="R4" t="n">
-        <v>6557554</v>
+        <v>6557478</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,17 +1007,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122263329</v>
+        <v>122263308</v>
       </c>
       <c r="B5" t="n">
-        <v>5489</v>
+        <v>57754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,34 +1026,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101410</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1065,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632303</v>
+        <v>632181</v>
       </c>
       <c r="R5" t="n">
-        <v>6557345</v>
+        <v>6557398</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1105,7 +1106,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal senvuxen tall.</t>
+          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,7 +1115,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122263308</v>
+        <v>122263382</v>
       </c>
       <c r="B6" t="n">
-        <v>57753</v>
+        <v>92150</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,25 +1145,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1171,13 +1171,12 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632181</v>
+        <v>632252</v>
       </c>
       <c r="R6" t="n">
-        <v>6557398</v>
+        <v>6557554</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1225,7 +1224,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Två födosökande kungsfåglar i senvuxna granar.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,6 +1233,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1245,17 +1245,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122263275</v>
+        <v>122263377</v>
       </c>
       <c r="B7" t="n">
-        <v>95011</v>
+        <v>92115</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,27 +1268,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1296,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632119</v>
+        <v>632243</v>
       </c>
       <c r="R7" t="n">
-        <v>6557502</v>
+        <v>6557542</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1336,7 +1335,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
+          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122263377</v>
+        <v>122263275</v>
       </c>
       <c r="B8" t="n">
-        <v>92114</v>
+        <v>95012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,26 +1379,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632243</v>
+        <v>632119</v>
       </c>
       <c r="R8" t="n">
-        <v>6557542</v>
+        <v>6557502</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gammal senvuxen tallskog med sparsamt inslag av olikåldrig gran med inslag av hänglavar. Stor del av marken är bergbunden.</t>
+          <t>Några mindre mosskuddar i anslutning till delvis berggrunden mark med gammal senvuxen tallskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
